--- a/artfynd/A 62731-2023 artfynd.xlsx
+++ b/artfynd/A 62731-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120257817</v>
+        <v>120257832</v>
       </c>
       <c r="B2" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>476796</v>
+        <v>476965</v>
       </c>
       <c r="R2" t="n">
-        <v>7069994</v>
+        <v>7070121</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120257839</v>
+        <v>120257821</v>
       </c>
       <c r="B3" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>476749</v>
+        <v>476997</v>
       </c>
       <c r="R3" t="n">
-        <v>7070034</v>
+        <v>7069990</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,6 +858,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120257838</v>
+        <v>120257819</v>
       </c>
       <c r="B4" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>476759</v>
+        <v>476878</v>
       </c>
       <c r="R4" t="n">
-        <v>7070031</v>
+        <v>7070000</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,6 +965,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120257822</v>
+        <v>120257838</v>
       </c>
       <c r="B5" t="n">
-        <v>57310</v>
+        <v>90598</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +1012,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477010</v>
+        <v>476759</v>
       </c>
       <c r="R5" t="n">
-        <v>7070001</v>
+        <v>7070031</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,11 +1072,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120257823</v>
+        <v>120257817</v>
       </c>
       <c r="B6" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1133,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477186</v>
+        <v>476796</v>
       </c>
       <c r="R6" t="n">
-        <v>7069941</v>
+        <v>7069994</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,7 +1178,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120257836</v>
+        <v>120257824</v>
       </c>
       <c r="B7" t="n">
-        <v>90558</v>
+        <v>57320</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1216,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>476714</v>
+        <v>477197</v>
       </c>
       <c r="R7" t="n">
-        <v>7069893</v>
+        <v>7069936</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1276,6 +1281,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1302,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120257824</v>
+        <v>120257836</v>
       </c>
       <c r="B8" t="n">
-        <v>57310</v>
+        <v>90576</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1318,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>477197</v>
+        <v>476714</v>
       </c>
       <c r="R8" t="n">
-        <v>7069936</v>
+        <v>7069893</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1378,11 +1388,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1409,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120257821</v>
+        <v>120257823</v>
       </c>
       <c r="B9" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1449,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>476997</v>
+        <v>477186</v>
       </c>
       <c r="R9" t="n">
-        <v>7069990</v>
+        <v>7069941</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1489,7 +1494,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1516,10 +1521,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120257819</v>
+        <v>120257822</v>
       </c>
       <c r="B10" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1556,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>476878</v>
+        <v>477010</v>
       </c>
       <c r="R10" t="n">
-        <v>7070000</v>
+        <v>7070001</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1596,7 +1601,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1623,10 +1628,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120257832</v>
+        <v>120257839</v>
       </c>
       <c r="B11" t="n">
-        <v>57310</v>
+        <v>90598</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1639,21 +1644,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1663,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>476965</v>
+        <v>476749</v>
       </c>
       <c r="R11" t="n">
-        <v>7070121</v>
+        <v>7070034</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1699,11 +1704,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 62731-2023 artfynd.xlsx
+++ b/artfynd/A 62731-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120257832</v>
+        <v>120257823</v>
       </c>
       <c r="B2" t="n">
         <v>57320</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>476965</v>
+        <v>477186</v>
       </c>
       <c r="R2" t="n">
-        <v>7070121</v>
+        <v>7069941</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120257821</v>
+        <v>120257817</v>
       </c>
       <c r="B3" t="n">
         <v>57320</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>476997</v>
+        <v>476796</v>
       </c>
       <c r="R3" t="n">
-        <v>7069990</v>
+        <v>7069994</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120257819</v>
+        <v>120257821</v>
       </c>
       <c r="B4" t="n">
         <v>57320</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>476878</v>
+        <v>476997</v>
       </c>
       <c r="R4" t="n">
-        <v>7070000</v>
+        <v>7069990</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120257838</v>
+        <v>120257832</v>
       </c>
       <c r="B5" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,21 +1012,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>476759</v>
+        <v>476965</v>
       </c>
       <c r="R5" t="n">
-        <v>7070031</v>
+        <v>7070121</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,6 +1072,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120257817</v>
+        <v>120257822</v>
       </c>
       <c r="B6" t="n">
         <v>57320</v>
@@ -1138,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>476796</v>
+        <v>477010</v>
       </c>
       <c r="R6" t="n">
-        <v>7069994</v>
+        <v>7070001</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1183,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120257824</v>
+        <v>120257838</v>
       </c>
       <c r="B7" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1226,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>477197</v>
+        <v>476759</v>
       </c>
       <c r="R7" t="n">
-        <v>7069936</v>
+        <v>7070031</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,11 +1286,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120257836</v>
+        <v>120257819</v>
       </c>
       <c r="B8" t="n">
-        <v>90576</v>
+        <v>57320</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>476714</v>
+        <v>476878</v>
       </c>
       <c r="R8" t="n">
-        <v>7069893</v>
+        <v>7070000</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1388,6 +1388,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1414,10 +1419,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120257823</v>
+        <v>120257839</v>
       </c>
       <c r="B9" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1430,21 +1435,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1454,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>477186</v>
+        <v>476749</v>
       </c>
       <c r="R9" t="n">
-        <v>7069941</v>
+        <v>7070034</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1490,11 +1495,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1521,10 +1521,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120257822</v>
+        <v>120257836</v>
       </c>
       <c r="B10" t="n">
-        <v>57320</v>
+        <v>90576</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1537,21 +1537,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1561,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>477010</v>
+        <v>476714</v>
       </c>
       <c r="R10" t="n">
-        <v>7070001</v>
+        <v>7069893</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1597,11 +1597,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1628,10 +1623,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120257839</v>
+        <v>120257824</v>
       </c>
       <c r="B11" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1644,21 +1639,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1668,10 +1663,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>476749</v>
+        <v>477197</v>
       </c>
       <c r="R11" t="n">
-        <v>7070034</v>
+        <v>7069936</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1704,6 +1699,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 62731-2023 artfynd.xlsx
+++ b/artfynd/A 62731-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120257823</v>
+        <v>120257821</v>
       </c>
       <c r="B2" t="n">
         <v>57320</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>477186</v>
+        <v>476997</v>
       </c>
       <c r="R2" t="n">
-        <v>7069941</v>
+        <v>7069990</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120257817</v>
+        <v>120257824</v>
       </c>
       <c r="B3" t="n">
         <v>57320</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>476796</v>
+        <v>477197</v>
       </c>
       <c r="R3" t="n">
-        <v>7069994</v>
+        <v>7069936</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120257821</v>
+        <v>120257817</v>
       </c>
       <c r="B4" t="n">
         <v>57320</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>476997</v>
+        <v>476796</v>
       </c>
       <c r="R4" t="n">
-        <v>7069990</v>
+        <v>7069994</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120257832</v>
+        <v>120257839</v>
       </c>
       <c r="B5" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,21 +1012,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>476965</v>
+        <v>476749</v>
       </c>
       <c r="R5" t="n">
-        <v>7070121</v>
+        <v>7070034</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,11 +1072,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1210,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120257838</v>
+        <v>120257823</v>
       </c>
       <c r="B7" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1226,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>476759</v>
+        <v>477186</v>
       </c>
       <c r="R7" t="n">
-        <v>7070031</v>
+        <v>7069941</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1286,6 +1281,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120257819</v>
+        <v>120257836</v>
       </c>
       <c r="B8" t="n">
-        <v>57320</v>
+        <v>90576</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>476878</v>
+        <v>476714</v>
       </c>
       <c r="R8" t="n">
-        <v>7070000</v>
+        <v>7069893</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1388,11 +1388,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1419,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120257839</v>
+        <v>120257819</v>
       </c>
       <c r="B9" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1435,21 +1430,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1459,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>476749</v>
+        <v>476878</v>
       </c>
       <c r="R9" t="n">
-        <v>7070034</v>
+        <v>7070000</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1495,6 +1490,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1521,10 +1521,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120257836</v>
+        <v>120257838</v>
       </c>
       <c r="B10" t="n">
-        <v>90576</v>
+        <v>90598</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1537,21 +1537,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1561,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>476714</v>
+        <v>476759</v>
       </c>
       <c r="R10" t="n">
-        <v>7069893</v>
+        <v>7070031</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1623,7 +1623,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120257824</v>
+        <v>120257832</v>
       </c>
       <c r="B11" t="n">
         <v>57320</v>
@@ -1663,10 +1663,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>477197</v>
+        <v>476965</v>
       </c>
       <c r="R11" t="n">
-        <v>7069936</v>
+        <v>7070121</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1727,6 +1727,750 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>120448415</v>
+      </c>
+      <c r="B12" t="n">
+        <v>90598</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Jontebodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>476955</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7070028</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>120448377</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Jontebodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>477096</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7070386</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>120448371</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Jontebodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>477183</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7070080</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>120448372</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Jontebodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>476940</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7070334</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>120448374</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Jontebodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>477006</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7070368</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>120448376</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Jontebodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>477088</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7070383</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>120448375</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Jontebodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>476996</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7070379</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 62731-2023 artfynd.xlsx
+++ b/artfynd/A 62731-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120257821</v>
+        <v>120257823</v>
       </c>
       <c r="B2" t="n">
         <v>57320</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>476997</v>
+        <v>477186</v>
       </c>
       <c r="R2" t="n">
-        <v>7069990</v>
+        <v>7069941</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120257824</v>
+        <v>120257819</v>
       </c>
       <c r="B3" t="n">
         <v>57320</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477197</v>
+        <v>476878</v>
       </c>
       <c r="R3" t="n">
-        <v>7069936</v>
+        <v>7070000</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120257817</v>
+        <v>120257822</v>
       </c>
       <c r="B4" t="n">
         <v>57320</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>476796</v>
+        <v>477010</v>
       </c>
       <c r="R4" t="n">
-        <v>7069994</v>
+        <v>7070001</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120257839</v>
+        <v>120257836</v>
       </c>
       <c r="B5" t="n">
-        <v>90598</v>
+        <v>90576</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,21 +1012,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>476749</v>
+        <v>476714</v>
       </c>
       <c r="R5" t="n">
-        <v>7070034</v>
+        <v>7069893</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,7 +1098,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120257822</v>
+        <v>120257817</v>
       </c>
       <c r="B6" t="n">
         <v>57320</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477010</v>
+        <v>476796</v>
       </c>
       <c r="R6" t="n">
-        <v>7070001</v>
+        <v>7069994</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120257823</v>
+        <v>120257821</v>
       </c>
       <c r="B7" t="n">
         <v>57320</v>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>477186</v>
+        <v>476997</v>
       </c>
       <c r="R7" t="n">
-        <v>7069941</v>
+        <v>7069990</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120257836</v>
+        <v>120257839</v>
       </c>
       <c r="B8" t="n">
-        <v>90576</v>
+        <v>90598</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>476714</v>
+        <v>476749</v>
       </c>
       <c r="R8" t="n">
-        <v>7069893</v>
+        <v>7070034</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1414,7 +1414,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120257819</v>
+        <v>120257824</v>
       </c>
       <c r="B9" t="n">
         <v>57320</v>
@@ -1454,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>476878</v>
+        <v>477197</v>
       </c>
       <c r="R9" t="n">
-        <v>7070000</v>
+        <v>7069936</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1521,10 +1521,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120257838</v>
+        <v>120257832</v>
       </c>
       <c r="B10" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1537,21 +1537,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1561,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>476759</v>
+        <v>476965</v>
       </c>
       <c r="R10" t="n">
-        <v>7070031</v>
+        <v>7070121</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1597,6 +1597,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1623,10 +1628,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120257832</v>
+        <v>120257838</v>
       </c>
       <c r="B11" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1639,21 +1644,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1663,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>476965</v>
+        <v>476759</v>
       </c>
       <c r="R11" t="n">
-        <v>7070121</v>
+        <v>7070031</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1699,11 +1704,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1730,10 +1730,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120448415</v>
+        <v>120448372</v>
       </c>
       <c r="B12" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1746,21 +1746,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1770,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>476955</v>
+        <v>476940</v>
       </c>
       <c r="R12" t="n">
-        <v>7070028</v>
+        <v>7070334</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1806,6 +1806,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1832,10 +1837,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120448377</v>
+        <v>120448415</v>
       </c>
       <c r="B13" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1848,21 +1853,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1872,10 +1877,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>477096</v>
+        <v>476955</v>
       </c>
       <c r="R13" t="n">
-        <v>7070386</v>
+        <v>7070028</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1908,11 +1913,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1939,7 +1939,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120448371</v>
+        <v>120448375</v>
       </c>
       <c r="B14" t="n">
         <v>57320</v>
@@ -1979,10 +1979,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>477183</v>
+        <v>476996</v>
       </c>
       <c r="R14" t="n">
-        <v>7070080</v>
+        <v>7070379</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2046,7 +2046,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120448372</v>
+        <v>120448377</v>
       </c>
       <c r="B15" t="n">
         <v>57320</v>
@@ -2086,10 +2086,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>476940</v>
+        <v>477096</v>
       </c>
       <c r="R15" t="n">
-        <v>7070334</v>
+        <v>7070386</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2153,7 +2153,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120448374</v>
+        <v>120448371</v>
       </c>
       <c r="B16" t="n">
         <v>57320</v>
@@ -2193,10 +2193,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>477006</v>
+        <v>477183</v>
       </c>
       <c r="R16" t="n">
-        <v>7070368</v>
+        <v>7070080</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2233,7 +2233,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2367,7 +2367,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120448375</v>
+        <v>120448374</v>
       </c>
       <c r="B18" t="n">
         <v>57320</v>
@@ -2407,10 +2407,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>476996</v>
+        <v>477006</v>
       </c>
       <c r="R18" t="n">
-        <v>7070379</v>
+        <v>7070368</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2447,7 +2447,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 62731-2023 artfynd.xlsx
+++ b/artfynd/A 62731-2023 artfynd.xlsx
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120257819</v>
+        <v>120257821</v>
       </c>
       <c r="B3" t="n">
         <v>57320</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>476878</v>
+        <v>476997</v>
       </c>
       <c r="R3" t="n">
-        <v>7070000</v>
+        <v>7069990</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120257836</v>
+        <v>120257839</v>
       </c>
       <c r="B5" t="n">
-        <v>90576</v>
+        <v>90598</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,21 +1012,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>476714</v>
+        <v>476749</v>
       </c>
       <c r="R5" t="n">
-        <v>7069893</v>
+        <v>7070034</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120257821</v>
+        <v>120257838</v>
       </c>
       <c r="B7" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>476997</v>
+        <v>476759</v>
       </c>
       <c r="R7" t="n">
-        <v>7069990</v>
+        <v>7070031</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,11 +1281,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120257839</v>
+        <v>120257819</v>
       </c>
       <c r="B8" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,21 +1323,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>476749</v>
+        <v>476878</v>
       </c>
       <c r="R8" t="n">
-        <v>7070034</v>
+        <v>7070000</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1388,6 +1383,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1414,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120257824</v>
+        <v>120257836</v>
       </c>
       <c r="B9" t="n">
-        <v>57320</v>
+        <v>90576</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1430,21 +1430,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1454,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>477197</v>
+        <v>476714</v>
       </c>
       <c r="R9" t="n">
-        <v>7069936</v>
+        <v>7069893</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1490,11 +1490,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1628,10 +1623,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120257838</v>
+        <v>120257824</v>
       </c>
       <c r="B11" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1644,21 +1639,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1668,10 +1663,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>476759</v>
+        <v>477197</v>
       </c>
       <c r="R11" t="n">
-        <v>7070031</v>
+        <v>7069936</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1704,6 +1699,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1730,7 +1730,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120448372</v>
+        <v>120448376</v>
       </c>
       <c r="B12" t="n">
         <v>57320</v>
@@ -1770,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>476940</v>
+        <v>477088</v>
       </c>
       <c r="R12" t="n">
-        <v>7070334</v>
+        <v>7070383</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1837,10 +1837,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120448415</v>
+        <v>120448374</v>
       </c>
       <c r="B13" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1853,21 +1853,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1877,10 +1877,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>476955</v>
+        <v>477006</v>
       </c>
       <c r="R13" t="n">
-        <v>7070028</v>
+        <v>7070368</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1913,6 +1913,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1939,10 +1944,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120448375</v>
+        <v>120448415</v>
       </c>
       <c r="B14" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1955,21 +1960,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1979,10 +1984,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>476996</v>
+        <v>476955</v>
       </c>
       <c r="R14" t="n">
-        <v>7070379</v>
+        <v>7070028</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2015,11 +2020,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2153,7 +2153,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120448371</v>
+        <v>120448375</v>
       </c>
       <c r="B16" t="n">
         <v>57320</v>
@@ -2193,10 +2193,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>477183</v>
+        <v>476996</v>
       </c>
       <c r="R16" t="n">
-        <v>7070080</v>
+        <v>7070379</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2260,7 +2260,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120448376</v>
+        <v>120448371</v>
       </c>
       <c r="B17" t="n">
         <v>57320</v>
@@ -2300,10 +2300,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>477088</v>
+        <v>477183</v>
       </c>
       <c r="R17" t="n">
-        <v>7070383</v>
+        <v>7070080</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2340,7 +2340,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2367,7 +2367,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120448374</v>
+        <v>120448372</v>
       </c>
       <c r="B18" t="n">
         <v>57320</v>
@@ -2407,10 +2407,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>477006</v>
+        <v>476940</v>
       </c>
       <c r="R18" t="n">
-        <v>7070368</v>
+        <v>7070334</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 62731-2023 artfynd.xlsx
+++ b/artfynd/A 62731-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120257823</v>
+        <v>120257836</v>
       </c>
       <c r="B2" t="n">
-        <v>57320</v>
+        <v>90576</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>477186</v>
+        <v>476714</v>
       </c>
       <c r="R2" t="n">
-        <v>7069941</v>
+        <v>7069893</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120257821</v>
+        <v>120257832</v>
       </c>
       <c r="B3" t="n">
         <v>57320</v>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>476997</v>
+        <v>476965</v>
       </c>
       <c r="R3" t="n">
-        <v>7069990</v>
+        <v>7070121</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120257822</v>
+        <v>120257817</v>
       </c>
       <c r="B4" t="n">
         <v>57320</v>
@@ -929,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477010</v>
+        <v>476796</v>
       </c>
       <c r="R4" t="n">
-        <v>7070001</v>
+        <v>7069994</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +964,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +991,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120257839</v>
+        <v>120257838</v>
       </c>
       <c r="B5" t="n">
         <v>90598</v>
@@ -1036,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>476749</v>
+        <v>476759</v>
       </c>
       <c r="R5" t="n">
-        <v>7070034</v>
+        <v>7070031</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120257817</v>
+        <v>120257839</v>
       </c>
       <c r="B6" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1114,21 +1109,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>476796</v>
+        <v>476749</v>
       </c>
       <c r="R6" t="n">
-        <v>7069994</v>
+        <v>7070034</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1174,11 +1169,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120257838</v>
+        <v>120257821</v>
       </c>
       <c r="B7" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1211,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>476759</v>
+        <v>476997</v>
       </c>
       <c r="R7" t="n">
-        <v>7070031</v>
+        <v>7069990</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,6 +1271,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,7 +1302,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120257819</v>
+        <v>120257822</v>
       </c>
       <c r="B8" t="n">
         <v>57320</v>
@@ -1347,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>476878</v>
+        <v>477010</v>
       </c>
       <c r="R8" t="n">
-        <v>7070000</v>
+        <v>7070001</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,7 +1382,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1414,10 +1409,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120257836</v>
+        <v>120257823</v>
       </c>
       <c r="B9" t="n">
-        <v>90576</v>
+        <v>57320</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1430,21 +1425,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1454,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>476714</v>
+        <v>477186</v>
       </c>
       <c r="R9" t="n">
-        <v>7069893</v>
+        <v>7069941</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1490,6 +1485,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1516,7 +1516,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120257832</v>
+        <v>120257819</v>
       </c>
       <c r="B10" t="n">
         <v>57320</v>
@@ -1556,10 +1556,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>476965</v>
+        <v>476878</v>
       </c>
       <c r="R10" t="n">
-        <v>7070121</v>
+        <v>7070000</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1730,7 +1730,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120448376</v>
+        <v>120448377</v>
       </c>
       <c r="B12" t="n">
         <v>57320</v>
@@ -1770,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>477088</v>
+        <v>477096</v>
       </c>
       <c r="R12" t="n">
-        <v>7070383</v>
+        <v>7070386</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1837,7 +1837,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120448374</v>
+        <v>120448376</v>
       </c>
       <c r="B13" t="n">
         <v>57320</v>
@@ -1877,10 +1877,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>477006</v>
+        <v>477088</v>
       </c>
       <c r="R13" t="n">
-        <v>7070368</v>
+        <v>7070383</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1944,10 +1944,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120448415</v>
+        <v>120448374</v>
       </c>
       <c r="B14" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1960,21 +1960,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1984,10 +1984,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>476955</v>
+        <v>477006</v>
       </c>
       <c r="R14" t="n">
-        <v>7070028</v>
+        <v>7070368</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2020,6 +2020,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2046,7 +2051,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120448377</v>
+        <v>120448375</v>
       </c>
       <c r="B15" t="n">
         <v>57320</v>
@@ -2086,10 +2091,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>477096</v>
+        <v>476996</v>
       </c>
       <c r="R15" t="n">
-        <v>7070386</v>
+        <v>7070379</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2126,7 +2131,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2153,7 +2158,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120448375</v>
+        <v>120448371</v>
       </c>
       <c r="B16" t="n">
         <v>57320</v>
@@ -2193,10 +2198,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>476996</v>
+        <v>477183</v>
       </c>
       <c r="R16" t="n">
-        <v>7070379</v>
+        <v>7070080</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2260,10 +2265,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120448371</v>
+        <v>120448415</v>
       </c>
       <c r="B17" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2276,21 +2281,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2300,10 +2305,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>477183</v>
+        <v>476955</v>
       </c>
       <c r="R17" t="n">
-        <v>7070080</v>
+        <v>7070028</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2336,11 +2341,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 62731-2023 artfynd.xlsx
+++ b/artfynd/A 62731-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120257836</v>
+        <v>120257823</v>
       </c>
       <c r="B2" t="n">
-        <v>90576</v>
+        <v>57320</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>476714</v>
+        <v>477186</v>
       </c>
       <c r="R2" t="n">
-        <v>7069893</v>
+        <v>7069941</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120257832</v>
+        <v>120257836</v>
       </c>
       <c r="B3" t="n">
-        <v>57320</v>
+        <v>90576</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>476965</v>
+        <v>476714</v>
       </c>
       <c r="R3" t="n">
-        <v>7070121</v>
+        <v>7069893</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,11 +858,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120257817</v>
+        <v>120257819</v>
       </c>
       <c r="B4" t="n">
         <v>57320</v>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>476796</v>
+        <v>476878</v>
       </c>
       <c r="R4" t="n">
-        <v>7069994</v>
+        <v>7070000</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +964,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120257838</v>
+        <v>120257821</v>
       </c>
       <c r="B5" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>476759</v>
+        <v>476997</v>
       </c>
       <c r="R5" t="n">
-        <v>7070031</v>
+        <v>7069990</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,6 +1067,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120257839</v>
+        <v>120257822</v>
       </c>
       <c r="B6" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>476749</v>
+        <v>477010</v>
       </c>
       <c r="R6" t="n">
-        <v>7070034</v>
+        <v>7070001</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,6 +1174,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1195,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120257821</v>
+        <v>120257839</v>
       </c>
       <c r="B7" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1211,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>476997</v>
+        <v>476749</v>
       </c>
       <c r="R7" t="n">
-        <v>7069990</v>
+        <v>7070034</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1271,11 +1281,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1302,7 +1307,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120257822</v>
+        <v>120257824</v>
       </c>
       <c r="B8" t="n">
         <v>57320</v>
@@ -1342,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>477010</v>
+        <v>477197</v>
       </c>
       <c r="R8" t="n">
-        <v>7070001</v>
+        <v>7069936</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1382,7 +1387,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1409,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120257823</v>
+        <v>120257838</v>
       </c>
       <c r="B9" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1425,21 +1430,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1449,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>477186</v>
+        <v>476759</v>
       </c>
       <c r="R9" t="n">
-        <v>7069941</v>
+        <v>7070031</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1485,11 +1490,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1516,7 +1516,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120257819</v>
+        <v>120257832</v>
       </c>
       <c r="B10" t="n">
         <v>57320</v>
@@ -1556,10 +1556,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>476878</v>
+        <v>476965</v>
       </c>
       <c r="R10" t="n">
-        <v>7070000</v>
+        <v>7070121</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1623,7 +1623,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120257824</v>
+        <v>120257817</v>
       </c>
       <c r="B11" t="n">
         <v>57320</v>
@@ -1663,10 +1663,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>477197</v>
+        <v>476796</v>
       </c>
       <c r="R11" t="n">
-        <v>7069936</v>
+        <v>7069994</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1730,7 +1730,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120448377</v>
+        <v>120448376</v>
       </c>
       <c r="B12" t="n">
         <v>57320</v>
@@ -1770,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>477096</v>
+        <v>477088</v>
       </c>
       <c r="R12" t="n">
-        <v>7070386</v>
+        <v>7070383</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1837,7 +1837,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120448376</v>
+        <v>120448377</v>
       </c>
       <c r="B13" t="n">
         <v>57320</v>
@@ -1877,10 +1877,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>477088</v>
+        <v>477096</v>
       </c>
       <c r="R13" t="n">
-        <v>7070383</v>
+        <v>7070386</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2051,7 +2051,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120448375</v>
+        <v>120448371</v>
       </c>
       <c r="B15" t="n">
         <v>57320</v>
@@ -2091,10 +2091,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>476996</v>
+        <v>477183</v>
       </c>
       <c r="R15" t="n">
-        <v>7070379</v>
+        <v>7070080</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2158,7 +2158,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120448371</v>
+        <v>120448372</v>
       </c>
       <c r="B16" t="n">
         <v>57320</v>
@@ -2198,10 +2198,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>477183</v>
+        <v>476940</v>
       </c>
       <c r="R16" t="n">
-        <v>7070080</v>
+        <v>7070334</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2238,7 +2238,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2367,7 +2367,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120448372</v>
+        <v>120448375</v>
       </c>
       <c r="B18" t="n">
         <v>57320</v>
@@ -2407,10 +2407,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>476940</v>
+        <v>476996</v>
       </c>
       <c r="R18" t="n">
-        <v>7070334</v>
+        <v>7070379</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2447,7 +2447,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
